--- a/excel_routes/route_ATZ_TUU_threats.xlsx
+++ b/excel_routes/route_ATZ_TUU_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +86,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -459,7 +468,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -537,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6317</v>
+        <v>6349</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10827</v>
+        <v>10882</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4510</v>
+        <v>-4533</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -582,13 +591,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6719</v>
+        <v>6753</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10827</v>
+        <v>10882</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4108</v>
+        <v>-4129</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>23</v>
@@ -623,26 +632,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-811</t>
+          <t>Air Arabia Egypt E5-599</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6719</v>
+        <v>6349</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10827</v>
+        <v>10882</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4108</v>
+        <v>-4533</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -658,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>27-FEB-26</t>
+          <t>20-FEB-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -672,13 +681,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6808</v>
+        <v>6753</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>10827</v>
+        <v>10882</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-4019</v>
+        <v>-4129</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>23</v>
@@ -695,6 +704,276 @@
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>27-FEB-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>6349</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>10882</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-4533</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>27-FEB-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>6842</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>10882</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-4040</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>27-MAR-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-117</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>12424</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>17278</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-4854</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>27-MAR-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-811</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>13354</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>17278</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-3924</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>27-MAR-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-599</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>13378</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>17278</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-3900</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>27-MAR-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-327</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-120</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>13940</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>17278</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-3338</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
